--- a/gte/nodes/LPC/compressor_stage_1_blade_rotor_coordinates_foil.xlsx
+++ b/gte/nodes/LPC/compressor_stage_1_blade_rotor_coordinates_foil.xlsx
@@ -349,7 +349,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>-1.3789333268917697E-17</v>
+        <v>1.3789333268917697E-17</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -357,7 +357,7 @@
         <v>0.0015525409042896332</v>
       </c>
       <c r="B2">
-        <v>0.0017664637878693143</v>
+        <v>0.0016678585761319585</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0031050818085792665</v>
       </c>
       <c r="B3">
-        <v>0.0027825089258028818</v>
+        <v>0.0025922076047275966</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0046576227128689</v>
       </c>
       <c r="B4">
-        <v>0.0036637569015056351</v>
+        <v>0.0033883228893957854</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0062101636171585329</v>
       </c>
       <c r="B5">
-        <v>0.0044451070887682144</v>
+        <v>0.0040907931337571752</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0077627045214481655</v>
       </c>
       <c r="B6">
-        <v>0.0051411554378299282</v>
+        <v>0.0047139335336480728</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0093152454257378</v>
       </c>
       <c r="B7">
-        <v>0.0057604444043512122</v>
+        <v>0.0052660403068260945</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.010867786330027433</v>
       </c>
       <c r="B8">
-        <v>0.0063082053574748049</v>
+        <v>0.0057521143555643592</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.012420327234317066</v>
       </c>
       <c r="B9">
-        <v>0.0067922324632667674</v>
+        <v>0.0061797519253917015</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.013972868138606698</v>
       </c>
       <c r="B10">
-        <v>0.0072208695060856937</v>
+        <v>0.0065571135042880382</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.015525409042896331</v>
       </c>
       <c r="B11">
-        <v>0.0076020959465369882</v>
+        <v>0.0068920212067819248</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.017077949947185967</v>
       </c>
       <c r="B12">
-        <v>0.0079403260079622517</v>
+        <v>0.0071887439867397906</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.0186304908514756</v>
       </c>
       <c r="B13">
-        <v>0.0082260772884010618</v>
+        <v>0.00743767652883092</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.020183031755765232</v>
       </c>
       <c r="B14">
-        <v>0.0084537774067636427</v>
+        <v>0.0076331343693210848</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.021735572660054867</v>
       </c>
       <c r="B15">
-        <v>0.0086473906907448168</v>
+        <v>0.0077989907200591811</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.023288113564344497</v>
       </c>
       <c r="B16">
-        <v>0.00882889506489679</v>
+        <v>0.0079571410396460616</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.024840654468634132</v>
       </c>
       <c r="B17">
-        <v>0.0089827861324166831</v>
+        <v>0.0080920120981073009</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.026393195372923766</v>
       </c>
       <c r="B18">
-        <v>0.0090889644788644</v>
+        <v>0.0081834458294333563</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.027945736277213397</v>
       </c>
       <c r="B19">
-        <v>0.0091464329406060838</v>
+        <v>0.0082304135120494556</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.029498277181503031</v>
       </c>
       <c r="B20">
-        <v>0.0091589699167094422</v>
+        <v>0.00823666876048953</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.031050818085792662</v>
       </c>
       <c r="B21">
-        <v>0.00913035380624218</v>
+        <v>0.0082059651892875014</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.0326033589900823</v>
       </c>
       <c r="B22">
-        <v>0.00906368070393697</v>
+        <v>0.0081413821937512537</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.034155899894371934</v>
       </c>
       <c r="B23">
-        <v>0.0089593174871863846</v>
+        <v>0.0080433022922844679</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.035708440798661568</v>
       </c>
       <c r="B24">
-        <v>0.00881694872904796</v>
+        <v>0.00791143378406479</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.0372609817029512</v>
       </c>
       <c r="B25">
-        <v>0.0086362590025792357</v>
+        <v>0.0077454849682698553</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.03881352260724083</v>
       </c>
       <c r="B26">
-        <v>0.0084168024542134769</v>
+        <v>0.0075450419752982065</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.040366063511530464</v>
       </c>
       <c r="B27">
-        <v>0.0081576115238868041</v>
+        <v>0.007309202260431984</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.0419186044158201</v>
       </c>
       <c r="B28">
-        <v>0.0078575882249110711</v>
+        <v>0.0070369411101742279</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.043471145320109733</v>
       </c>
       <c r="B29">
-        <v>0.0075156345705981236</v>
+        <v>0.0067272338110279809</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.045023686224399367</v>
       </c>
       <c r="B30">
-        <v>0.0071311205114807262</v>
+        <v>0.0063795333878534062</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.046576227128688995</v>
       </c>
       <c r="B31">
-        <v>0.0067052877469753122</v>
+        <v>0.0059952038189391588</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.048128768032978629</v>
       </c>
       <c r="B32">
-        <v>0.0062398459137192252</v>
+        <v>0.0055760868209310142</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.049681308937268263</v>
       </c>
       <c r="B33">
-        <v>0.0057365046483498156</v>
+        <v>0.00512402411047475</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.0512338498415579</v>
       </c>
       <c r="B34">
-        <v>0.0051961466592248783</v>
+        <v>0.0046400441254114471</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.052786390745847532</v>
       </c>
       <c r="B35">
-        <v>0.0046163469415839969</v>
+        <v>0.0041219221883634022</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.054338931650137159</v>
       </c>
       <c r="B36">
-        <v>0.0039938535623872057</v>
+        <v>0.0035666203431482186</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.055891472554426794</v>
       </c>
       <c r="B37">
-        <v>0.0033254145885945308</v>
+        <v>0.0029711006335834912</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.057444013458716428</v>
       </c>
       <c r="B38">
-        <v>0.0026057911483118542</v>
+        <v>0.0023303550405464925</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.058996554363006062</v>
       </c>
       <c r="B39">
-        <v>0.0018217966142284536</v>
+        <v>0.0016314952931531688</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.0605490952672957</v>
       </c>
       <c r="B40">
-        <v>0.000958257420179454</v>
+        <v>0.00085966305757913589</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -669,7 +669,7 @@
         <v>0.062101636171585324</v>
       </c>
       <c r="B41">
-        <v>-1.3573874936590858E-17</v>
+        <v>1.3789333268917697E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -677,7 +677,7 @@
         <v>0.062101636171585324</v>
       </c>
       <c r="B42">
-        <v>-1.3789333268917697E-17</v>
+        <v>1.3789333268917697E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.0605490952672957</v>
       </c>
       <c r="B43">
-        <v>0.00027686623591383997</v>
+        <v>0.00017827187331352195</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.058996554363006062</v>
       </c>
       <c r="B44">
-        <v>0.00057603779262645411</v>
+        <v>0.00038573647155116939</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.057444013458716428</v>
       </c>
       <c r="B45">
-        <v>0.00088384901273712063</v>
+        <v>0.00060841290497175868</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.055891472554426794</v>
       </c>
       <c r="B46">
-        <v>0.0011866342388451325</v>
+        <v>0.00083232028383409273</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.054338931650137159</v>
       </c>
       <c r="B47">
-        <v>0.00147264202185186</v>
+        <v>0.0010454088026128725</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.052786390745847532</v>
       </c>
       <c r="B48">
-        <v>0.0017377777458669832</v>
+        <v>0.0012433529926463886</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.0512338498415579</v>
       </c>
       <c r="B49">
-        <v>0.0019798610033022615</v>
+        <v>0.0014237584694888304</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.049681308937268263</v>
       </c>
       <c r="B50">
-        <v>0.0021967113865694523</v>
+        <v>0.0015842308486943865</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.048128768032978629</v>
       </c>
       <c r="B51">
-        <v>0.0023869117498250543</v>
+        <v>0.0017231526570368435</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.046576227128688995</v>
       </c>
       <c r="B52">
-        <v>0.0025520979942045365</v>
+        <v>0.0018420140661683838</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.045023686224399367</v>
       </c>
       <c r="B53">
-        <v>0.0026946692825881081</v>
+        <v>0.0019430821589607871</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.043471145320109733</v>
       </c>
       <c r="B54">
-        <v>0.0028170247778559789</v>
+        <v>0.0020286240182858361</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.0419186044158201</v>
       </c>
       <c r="B55">
-        <v>0.0029210461047589988</v>
+        <v>0.0021003989900221561</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.040366063511530464</v>
       </c>
       <c r="B56">
-        <v>0.003006544735530576</v>
+        <v>0.0021581354720757559</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.03881352260724083</v>
       </c>
       <c r="B57">
-        <v>0.0030728146042747597</v>
+        <v>0.0022010541253594906</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.0372609817029512</v>
       </c>
       <c r="B58">
-        <v>0.003119149645095597</v>
+        <v>0.0022283756107862158</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.035708440798661568</v>
       </c>
       <c r="B59">
-        <v>0.0031449303331062698</v>
+        <v>0.0022394153881231003</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.034155899894371934</v>
       </c>
       <c r="B60">
-        <v>0.0031498833074564895</v>
+        <v>0.0022338681125545746</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.0326033589900823</v>
       </c>
       <c r="B61">
-        <v>0.0031338217483051012</v>
+        <v>0.0022115232381193831</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.031050818085792662</v>
       </c>
       <c r="B62">
-        <v>0.0030965588358109488</v>
+        <v>0.0021721702188562714</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.029498277181503031</v>
       </c>
       <c r="B63">
-        <v>0.0030385462698152917</v>
+        <v>0.0021162451135953784</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.027945736277213397</v>
       </c>
       <c r="B64">
-        <v>0.0029627898288890494</v>
+        <v>0.002046770400332422</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.026393195372923766</v>
       </c>
       <c r="B65">
-        <v>0.0028729338112855581</v>
+        <v>0.0019674151618545147</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.024840654468634132</v>
       </c>
       <c r="B66">
-        <v>0.002772622515258151</v>
+        <v>0.0018818484809487693</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.023288113564344497</v>
       </c>
       <c r="B67">
-        <v>0.0026606884749277864</v>
+        <v>0.0017889344496770563</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.021735572660054867</v>
       </c>
       <c r="B68">
-        <v>0.002516717167885913</v>
+        <v>0.0016683171972002771</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.020183031755765232</v>
       </c>
       <c r="B69">
-        <v>0.0023248353641602409</v>
+        <v>0.0015041923267176838</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.0186304908514756</v>
       </c>
       <c r="B70">
-        <v>0.0021065820600530438</v>
+        <v>0.0013181813004829008</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.017077949947185967</v>
       </c>
       <c r="B71">
-        <v>0.0018854385715062656</v>
+        <v>0.0011338565502838048</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.015525409042896331</v>
       </c>
       <c r="B72">
-        <v>0.0016552432667459776</v>
+        <v>0.00094516852699091426</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.013972868138606698</v>
       </c>
       <c r="B73">
-        <v>0.0014058707568041847</v>
+        <v>0.000742114755006529</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.012420327234317066</v>
       </c>
       <c r="B74">
-        <v>0.0011409835716525015</v>
+        <v>0.00052850303377743586</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.010867786330027433</v>
       </c>
       <c r="B75">
-        <v>0.00086775185353866807</v>
+        <v>0.00031166085162822281</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0093152454257378</v>
       </c>
       <c r="B76">
-        <v>0.00059358827487531319</v>
+        <v>9.9184177350194946E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0077627045214481655</v>
       </c>
       <c r="B77">
-        <v>0.00032528901348578891</v>
+        <v>-0.00010193289069606642</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0062101636171585329</v>
       </c>
       <c r="B78">
-        <v>6.6941738671449184E-05</v>
+        <v>-0.00028737221633959043</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0046576227128689</v>
       </c>
       <c r="B79">
-        <v>-0.00017412421389833823</v>
+        <v>-0.00044955822600818777</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0031050818085792665</v>
       </c>
       <c r="B80">
-        <v>-0.00038467451894796912</v>
+        <v>-0.00057497584002325422</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0015525409042896332</v>
       </c>
       <c r="B81">
-        <v>-0.00053129675047934252</v>
+        <v>-0.00062990196221669834</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-1.3789333268917697E-17</v>
+        <v>1.3789333268917697E-17</v>
       </c>
     </row>
   </sheetData>
@@ -1023,7 +1023,7 @@
         <v>0.0018017730829636811</v>
       </c>
       <c r="B2">
-        <v>0.000827420196602657</v>
+        <v>0.00076622537021123617</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0036035461659273621</v>
       </c>
       <c r="B3">
-        <v>0.0013078616282574465</v>
+        <v>0.0011887966315018924</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0054053192488910436</v>
       </c>
       <c r="B4">
-        <v>0.0017267849696027732</v>
+        <v>0.0015531441329566097</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0072070923318547243</v>
       </c>
       <c r="B5">
-        <v>0.0021001020542747643</v>
+        <v>0.0018751512663924145</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0090088654148184049</v>
       </c>
       <c r="B6">
-        <v>0.0024343253669077496</v>
+        <v>0.002161303813815409</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.010810638497782087</v>
       </c>
       <c r="B7">
-        <v>0.00273318749828434</v>
+        <v>0.0024153098709024587</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.012612411580745768</v>
       </c>
       <c r="B8">
-        <v>0.0029988979876152881</v>
+        <v>0.0026393555739197662</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.014414184663709449</v>
       </c>
       <c r="B9">
-        <v>0.0032348852389172556</v>
+        <v>0.0028368483094069808</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.016215957746673129</v>
       </c>
       <c r="B10">
-        <v>0.0034448460711167437</v>
+        <v>0.0030114650289302463</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.01801773082963681</v>
       </c>
       <c r="B11">
-        <v>0.0036323320979737093</v>
+        <v>0.0031667396938882333</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.019819503912600494</v>
       </c>
       <c r="B12">
-        <v>0.0037992511401859514</v>
+        <v>0.0033045635582443114</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.021621276995564175</v>
       </c>
       <c r="B13">
-        <v>0.0039410810513691831</v>
+        <v>0.0034204000363881205</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.023423050078527855</v>
       </c>
       <c r="B14">
-        <v>0.00405512506504656</v>
+        <v>0.0035115390173496457</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.025224823161491536</v>
       </c>
       <c r="B15">
-        <v>0.0041524179014530843</v>
+        <v>0.0035890041282939916</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.027026596244455213</v>
       </c>
       <c r="B16">
-        <v>0.0042430805155943881</v>
+        <v>0.0036629061752231924</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.028828369327418897</v>
       </c>
       <c r="B17">
-        <v>0.0043198473148467822</v>
+        <v>0.0037259709413518952</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.030630142410382581</v>
       </c>
       <c r="B18">
-        <v>0.00437332965396126</v>
+        <v>0.0037688023812923583</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.032431915493346258</v>
       </c>
       <c r="B19">
-        <v>0.0044030332248168689</v>
+        <v>0.0037909021580346844</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.034233688576309942</v>
       </c>
       <c r="B20">
-        <v>0.0044106873035746749</v>
+        <v>0.003793996361663437</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.03603546165927362</v>
       </c>
       <c r="B21">
-        <v>0.0043980211663957394</v>
+        <v>0.0037798110822631781</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.037837234742237304</v>
       </c>
       <c r="B22">
-        <v>0.0043664554180734057</v>
+        <v>0.0037497647803003725</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.039639007825200988</v>
       </c>
       <c r="B23">
-        <v>0.004316175977930139</v>
+        <v>0.0037040453977690816</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.041440780908164665</v>
       </c>
       <c r="B24">
-        <v>0.0042470600939206833</v>
+        <v>0.0036425332470452691</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.043242553991128349</v>
       </c>
       <c r="B25">
-        <v>0.0041589850139997844</v>
+        <v>0.0035651086405048969</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.045044327074092026</v>
       </c>
       <c r="B26">
-        <v>0.0040517755925591689</v>
+        <v>0.0034716005090799505</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.04684610015705571</v>
       </c>
       <c r="B27">
-        <v>0.0039250471097384927</v>
+        <v>0.0033616322579264981</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.048647873240019388</v>
       </c>
       <c r="B28">
-        <v>0.0037783624521143936</v>
+        <v>0.0032347759107566334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.050449646322983072</v>
       </c>
       <c r="B29">
-        <v>0.0036112845062635096</v>
+        <v>0.0030906034912824474</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.052251419405946756</v>
       </c>
       <c r="B30">
-        <v>0.0034236028054535146</v>
+        <v>0.0029289147180012903</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.054053192488910426</v>
       </c>
       <c r="B31">
-        <v>0.0032160134697162223</v>
+        <v>0.0027504200885515458</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.05585496557187411</v>
       </c>
       <c r="B32">
-        <v>0.0029894392657744792</v>
+        <v>0.0025560577953568546</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.057656738654837794</v>
       </c>
       <c r="B33">
-        <v>0.0027448029603511343</v>
+        <v>0.0023467660308408595</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.059458511737801478</v>
       </c>
       <c r="B34">
-        <v>0.0024826559841847036</v>
+        <v>0.0021231127946050514</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.061260284820765162</v>
       </c>
       <c r="B35">
-        <v>0.00220206442407637</v>
+        <v>0.0018841853149623206</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.063062057903728833</v>
       </c>
       <c r="B36">
-        <v>0.0019017230308429867</v>
+        <v>0.0016287006274034082</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.064863830986692517</v>
       </c>
       <c r="B37">
-        <v>0.0015803265553014016</v>
+        <v>0.0013553757674190519</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.0666656040696562</v>
       </c>
       <c r="B38">
-        <v>0.0012356621725436222</v>
+        <v>0.0010620212812337115</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.068467377152619885</v>
       </c>
       <c r="B39">
-        <v>0.00086188675476227435</v>
+        <v>0.0007428217580067205</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.070269150235583569</v>
       </c>
       <c r="B40">
-        <v>0.00045224959842513925</v>
+        <v>0.000391055297631132</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.070269150235583569</v>
       </c>
       <c r="B43">
-        <v>0.00013593914466861936</v>
+        <v>7.4744843874612022E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.068467377152619885</v>
       </c>
       <c r="B44">
-        <v>0.00028358966605425239</v>
+        <v>0.00016452466929869853</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.0666656040696562</v>
       </c>
       <c r="B45">
-        <v>0.00043631473332903284</v>
+        <v>0.00026267384201912207</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.064863830986692517</v>
       </c>
       <c r="B46">
-        <v>0.000587477515665095</v>
+        <v>0.00036252672778274526</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.063062057903728833</v>
       </c>
       <c r="B47">
-        <v>0.000731344568634939</v>
+        <v>0.00045832216519536048</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.061260284820765162</v>
       </c>
       <c r="B48">
-        <v>0.00086579599341252741</v>
+        <v>0.00054791688429847794</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.059458511737801478</v>
       </c>
       <c r="B49">
-        <v>0.00098961527757219061</v>
+        <v>0.00063007208799253868</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.057656738654837794</v>
       </c>
       <c r="B50">
-        <v>0.0011015859086882572</v>
+        <v>0.00070354897917798232</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.05585496557187411</v>
       </c>
       <c r="B51">
-        <v>0.0012008582247842413</v>
+        <v>0.00076747675436661692</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.054053192488910426</v>
       </c>
       <c r="B52">
-        <v>0.0012880499656803988</v>
+        <v>0.00082245658451572212</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.052251419405946756</v>
       </c>
       <c r="B53">
-        <v>0.00136414572164617</v>
+        <v>0.0008694576341939451</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.050449646322983072</v>
       </c>
       <c r="B54">
-        <v>0.0014301300829509967</v>
+        <v>0.000909449067969934</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.048647873240019388</v>
       </c>
       <c r="B55">
-        <v>0.0014867568163643538</v>
+        <v>0.00094317027500659368</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.04684610015705571</v>
       </c>
       <c r="B56">
-        <v>0.0015338563946558559</v>
+        <v>0.00097044154284386161</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.045044327074092026</v>
       </c>
       <c r="B57">
-        <v>0.0015710284670951515</v>
+        <v>0.000990853383615933</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.043242553991128349</v>
       </c>
       <c r="B58">
-        <v>0.00159787268295189</v>
+        <v>0.0010039963094570028</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.041440780908164665</v>
       </c>
       <c r="B59">
-        <v>0.0016140370170675553</v>
+        <v>0.0010095101701921411</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.039639007825200988</v>
       </c>
       <c r="B60">
-        <v>0.0016193627465709742</v>
+        <v>0.0010072321664099174</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.037837234742237304</v>
       </c>
       <c r="B61">
-        <v>0.0016137394741628083</v>
+        <v>0.00099704883638977531</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.03603546165927362</v>
       </c>
       <c r="B62">
-        <v>0.0015970568025437195</v>
+        <v>0.0009788467184111587</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.034233688576309942</v>
       </c>
       <c r="B63">
-        <v>0.0015695088063539559</v>
+        <v>0.00095281786444271761</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.032431915493346258</v>
       </c>
       <c r="B64">
-        <v>0.0015325074479921104</v>
+        <v>0.00092037638120992537</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.030630142410382581</v>
       </c>
       <c r="B65">
-        <v>0.0014877691617963629</v>
+        <v>0.00088324188912746143</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.028828369327418897</v>
       </c>
       <c r="B66">
-        <v>0.0014370103821048925</v>
+        <v>0.00084313400861000523</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.027026596244455213</v>
       </c>
       <c r="B67">
-        <v>0.0013797205684887273</v>
+        <v>0.00079954622811753164</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.025224823161491536</v>
       </c>
       <c r="B68">
-        <v>0.001306481281450291</v>
+        <v>0.00074306750829119823</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.023423050078527855</v>
       </c>
       <c r="B69">
-        <v>0.0012099922201995589</v>
+        <v>0.00066640617250264479</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.021621276995564175</v>
       </c>
       <c r="B70">
-        <v>0.0011003335378453251</v>
+        <v>0.00057965252286426236</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.019819503912600494</v>
       </c>
       <c r="B71">
-        <v>0.00098849538534855259</v>
+        <v>0.00049380780340691323</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.01801773082963681</v>
       </c>
       <c r="B72">
-        <v>0.0008717274511800756</v>
+        <v>0.00040613504709459977</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.016215957746673129</v>
       </c>
       <c r="B73">
-        <v>0.00074544969580081033</v>
+        <v>0.00031206865361431294</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.014414184663709449</v>
       </c>
       <c r="B74">
-        <v>0.000611503630122136</v>
+        <v>0.00021346670061186114</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.012612411580745768</v>
       </c>
       <c r="B75">
-        <v>0.00047337027870311585</v>
+        <v>0.00011382786500759361</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.010810638497782087</v>
       </c>
       <c r="B76">
-        <v>0.00033466717024308756</v>
+        <v>1.6789542861206235E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0090088654148184049</v>
       </c>
       <c r="B77">
-        <v>0.0001987389239207198</v>
+        <v>-7.4282629171620949E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0072070923318547243</v>
       </c>
       <c r="B78">
-        <v>6.7702016691732452E-05</v>
+        <v>-0.0001572487711906173</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0054053192488910436</v>
       </c>
       <c r="B79">
-        <v>-5.4808254831714684E-05</v>
+        <v>-0.0002284490914778781</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0036035461659273621</v>
       </c>
       <c r="B80">
-        <v>-0.00016238520744091717</v>
+        <v>-0.00028145020419647124</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0018017730829636811</v>
       </c>
       <c r="B81">
-        <v>-0.00023922946851184215</v>
+        <v>-0.000300424294903263</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0020183031755765233</v>
       </c>
       <c r="B2">
-        <v>0.00062779438059189046</v>
+        <v>0.000581982893614649</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0040366063511530466</v>
       </c>
       <c r="B3">
-        <v>0.00096777842005026885</v>
+        <v>0.0008785443369778563</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.00605490952672957</v>
       </c>
       <c r="B4">
-        <v>0.00125973726736921</v>
+        <v>0.0011294631751332137</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0080732127023060932</v>
       </c>
       <c r="B5">
-        <v>0.001517001856134591</v>
+        <v>0.0013480643931252259</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.010091515877882616</v>
       </c>
       <c r="B6">
-        <v>0.001745008660529841</v>
+        <v>0.001539778849594872</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.012109819053459141</v>
       </c>
       <c r="B7">
-        <v>0.0019468615225341568</v>
+        <v>0.0017077052013006525</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.014128122229035664</v>
       </c>
       <c r="B8">
-        <v>0.0021243861311985978</v>
+        <v>0.001853664168216391</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.016146425404612186</v>
       </c>
       <c r="B9">
-        <v>0.0022804352714807588</v>
+        <v>0.0019805040431423657</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.018164728580188711</v>
       </c>
       <c r="B10">
-        <v>0.002418088724747931</v>
+        <v>0.0020913003482914325</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.020183031755765232</v>
       </c>
       <c r="B11">
-        <v>0.0025403071620996652</v>
+        <v>0.0021890099507003162</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.022201334931341757</v>
       </c>
       <c r="B12">
-        <v>0.0026486716658033729</v>
+        <v>0.0022752103537285362</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.024219638106918281</v>
       </c>
       <c r="B13">
-        <v>0.0027393640730656618</v>
+        <v>0.0023460802612029277</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.026237941282494803</v>
       </c>
       <c r="B14">
-        <v>0.0028101012127047078</v>
+        <v>0.0023993336002637016</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.028256244458071327</v>
       </c>
       <c r="B15">
-        <v>0.0028701391250457752</v>
+        <v>0.0024442239908372492</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.030274547633647848</v>
       </c>
       <c r="B16">
-        <v>0.0029279674040215142</v>
+        <v>0.0024892388087870668</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.032292850809224373</v>
       </c>
       <c r="B17">
-        <v>0.0029774706464870339</v>
+        <v>0.0025282607609388905</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.0343111539848009</v>
       </c>
       <c r="B18">
-        <v>0.0030107514130897658</v>
+        <v>0.0025533907844224497</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.036329457160377422</v>
       </c>
       <c r="B19">
-        <v>0.0030273891167239696</v>
+        <v>0.0025642074066212104</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.038347760335953947</v>
       </c>
       <c r="B20">
-        <v>0.0030288323833456109</v>
+        <v>0.0025621585524820759</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.040366063511530464</v>
       </c>
       <c r="B21">
-        <v>0.0030165298389106571</v>
+        <v>0.0025486921469519458</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.042384366687106989</v>
       </c>
       <c r="B22">
-        <v>0.0029916721561895456</v>
+        <v>0.0025249983910783907</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.044402669862683514</v>
       </c>
       <c r="B23">
-        <v>0.0029544181952106041</v>
+        <v>0.0024912365903116541</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.046420973038260038</v>
       </c>
       <c r="B24">
-        <v>0.0029046688628166328</v>
+        <v>0.0024473083262026483</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.048439276213836563</v>
       </c>
       <c r="B25">
-        <v>0.0028423250658504294</v>
+        <v>0.002393115180302286</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.050457579389413081</v>
       </c>
       <c r="B26">
-        <v>0.0027672450243423456</v>
+        <v>0.0023285162684029523</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.052475882564989605</v>
       </c>
       <c r="B27">
-        <v>0.0026791162110729309</v>
+        <v>0.0022532008432629238</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.05449418574056613</v>
       </c>
       <c r="B28">
-        <v>0.0025775834120102875</v>
+        <v>0.0021668156918819505</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.056512488916142654</v>
       </c>
       <c r="B29">
-        <v>0.0024622914131225155</v>
+        <v>0.0020690076012597819</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.058530792091719179</v>
       </c>
       <c r="B30">
-        <v>0.0023330767860805452</v>
+        <v>0.0019596153679113347</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.0605490952672957</v>
       </c>
       <c r="B31">
-        <v>0.0021905432453666156</v>
+        <v>0.0018392458264121859</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.062567398442872221</v>
       </c>
       <c r="B32">
-        <v>0.0020354862911657937</v>
+        <v>0.0017086978208530779</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.064585701618448746</v>
       </c>
       <c r="B33">
-        <v>0.0018687014236631479</v>
+        <v>0.0015687701953247548</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.066604004794025271</v>
       </c>
       <c r="B34">
-        <v>0.0016906736579926696</v>
+        <v>0.0014199515430230114</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.0686223079696018</v>
       </c>
       <c r="B35">
-        <v>0.001500646069084051</v>
+        <v>0.0012614894535638496</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.0706406111451783</v>
       </c>
       <c r="B36">
-        <v>0.0012975512468159076</v>
+        <v>0.0010923212656683248</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.072658914320754844</v>
       </c>
       <c r="B37">
-        <v>0.0010803217810668546</v>
+        <v>0.00091138431805748953</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.074677217496331369</v>
       </c>
       <c r="B38">
-        <v>0.000847129179202478</v>
+        <v>0.0007168550790636138</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.0766955206719079</v>
       </c>
       <c r="B39">
-        <v>0.00059310061853624213</v>
+        <v>0.00050386653546382969</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.078713823847484418</v>
       </c>
       <c r="B40">
-        <v>0.00031260219386858046</v>
+        <v>0.00026679080364648496</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.080732127023060929</v>
       </c>
       <c r="B41">
-        <v>-7.1774556956378249E-17</v>
+        <v>-7.1704532998372032E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.080732127023060929</v>
       </c>
       <c r="B42">
-        <v>-7.1704532998372032E-17</v>
+        <v>-7.1695780003621248E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.078713823847484418</v>
       </c>
       <c r="B43">
-        <v>4.6859632004991045E-05</v>
+        <v>1.0482417828955414E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.0766955206719079</v>
       </c>
       <c r="B44">
-        <v>0.0001072546781114624</v>
+        <v>1.8020595039049985E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.074677217496331369</v>
       </c>
       <c r="B45">
-        <v>0.00017557174632833186</v>
+        <v>4.5297646189467518E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.072658914320754844</v>
       </c>
       <c r="B46">
-        <v>0.00024619744466458914</v>
+        <v>7.7259981655223987E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.0706406111451783</v>
       </c>
       <c r="B47">
-        <v>0.00031427874600712259</v>
+        <v>0.00010904876485953986</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.0686223079696018</v>
       </c>
       <c r="B48">
-        <v>0.000378004082754415</v>
+        <v>0.00013884746723421404</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.066604004794025271</v>
       </c>
       <c r="B49">
-        <v>0.000436322252182849</v>
+        <v>0.00016560013721319045</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.064585701618448746</v>
       </c>
       <c r="B50">
-        <v>0.00048818205156880579</v>
+        <v>0.00018825082323041271</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.062567398442872221</v>
       </c>
       <c r="B51">
-        <v>0.000532841967247067</v>
+        <v>0.00020605349693435116</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.0605490952672957</v>
       </c>
       <c r="B52">
-        <v>0.00057079924178601307</v>
+        <v>0.00021950182283158334</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.058530792091719179</v>
       </c>
       <c r="B53">
-        <v>0.00060286080681242371</v>
+        <v>0.00022939938864321345</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.056512488916142654</v>
       </c>
       <c r="B54">
-        <v>0.00062983359395307921</v>
+        <v>0.00023654978209034582</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.05449418574056613</v>
       </c>
       <c r="B55">
-        <v>0.00065233198515097927</v>
+        <v>0.00024156426502264223</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.052475882564989605</v>
       </c>
       <c r="B56">
-        <v>0.00067020016361400215</v>
+        <v>0.0002442847958039948</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.050457579389413081</v>
       </c>
       <c r="B57">
-        <v>0.00068308976286624631</v>
+        <v>0.00024436100692685304</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.048439276213836563</v>
       </c>
       <c r="B58">
-        <v>0.00069065241643181019</v>
+        <v>0.00024144253088366672</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.046420973038260038</v>
       </c>
       <c r="B59">
-        <v>0.000692581688399374</v>
+        <v>0.00023522115178539003</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.044402669862683514</v>
       </c>
       <c r="B60">
-        <v>0.00068873886511594616</v>
+        <v>0.00022555726021699596</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.042384366687106989</v>
       </c>
       <c r="B61">
-        <v>0.00067902716349311717</v>
+        <v>0.00021235339838196216</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.040366063511530464</v>
       </c>
       <c r="B62">
-        <v>0.00066334980044247742</v>
+        <v>0.00019551210848376625</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.038347760335953947</v>
       </c>
       <c r="B63">
-        <v>0.00064186716105689228</v>
+        <v>0.00017519333019335698</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.036329457160377422</v>
       </c>
       <c r="B64">
-        <v>0.000615768303154326</v>
+        <v>0.00015258659305156721</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.0343111539848009</v>
       </c>
       <c r="B65">
-        <v>0.00058649945273401768</v>
+        <v>0.00012913882406670116</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.032292850809224373</v>
       </c>
       <c r="B66">
-        <v>0.00055550683579520626</v>
+        <v>0.00010629695024706269</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.030274547633647848</v>
       </c>
       <c r="B67">
-        <v>0.00052236683393360231</v>
+        <v>8.36382386991549E-05</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.028256244458071327</v>
       </c>
       <c r="B68">
-        <v>0.00047917645113080285</v>
+        <v>5.3261316922276512E-05</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.026237941282494803</v>
       </c>
       <c r="B69">
-        <v>0.00041981381608938151</v>
+        <v>9.0462036483753266E-06</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.024219638106918281</v>
       </c>
       <c r="B70">
-        <v>0.00035276093400993442</v>
+        <v>-4.0522877852799109E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.022201334931341757</v>
       </c>
       <c r="B71">
-        <v>0.00028726556558553824</v>
+        <v>-8.6195746489298311E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.020183031755765232</v>
       </c>
       <c r="B72">
-        <v>0.00022103461698117063</v>
+        <v>-0.00013026259441817776</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.018164728580188711</v>
       </c>
       <c r="B73">
-        <v>0.00015023921252814247</v>
+        <v>-0.00017654916392835583</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.016146425404612186</v>
       </c>
       <c r="B74">
-        <v>7.6448203751195E-05</v>
+        <v>-0.00022348302458719807</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.014128122229035664</v>
       </c>
       <c r="B75">
-        <v>2.6092646635044115E-06</v>
+        <v>-0.00026811269831870233</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.012109819053459141</v>
       </c>
       <c r="B76">
-        <v>-6.8212367961444033E-05</v>
+        <v>-0.00030736868919494837</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.010091515877882616</v>
       </c>
       <c r="B77">
-        <v>-0.00013317924496437323</v>
+        <v>-0.00033840905589934225</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0080732127023060932</v>
       </c>
       <c r="B78">
-        <v>-0.00019048263040314726</v>
+        <v>-0.00035942009341251242</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.00605490952672957</v>
       </c>
       <c r="B79">
-        <v>-0.00023703636763833941</v>
+        <v>-0.0003673104598743358</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0040366063511530466</v>
       </c>
       <c r="B80">
-        <v>-0.00026742312340256294</v>
+        <v>-0.00035665720647497554</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0020183031755765233</v>
       </c>
       <c r="B81">
-        <v>-0.0002683322293640857</v>
+        <v>-0.0003141437163413272</v>
       </c>
     </row>
     <row r="82" spans="1:2">
